--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
   <si>
     <t>序号ID</t>
   </si>
@@ -182,10 +182,16 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
-  </si>
-  <si>
-    <t>map&lt;string{_}string&gt;{;}</t>
+    <t>list&lt;list&lt;int&gt;{_}&gt;{;}</t>
+  </si>
+  <si>
+    <t>list&lt;string&gt;{_}</t>
+  </si>
+  <si>
+    <t>list&lt;list&lt;string&gt;{_}&gt;{;}</t>
+  </si>
+  <si>
+    <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
     <t>bool</t>
@@ -237,6 +243,12 @@
   </si>
   <si>
     <t>UICashCow_0</t>
+  </si>
+  <si>
+    <t>2025/10/1 0:00:00</t>
+  </si>
+  <si>
+    <t>2025/10/31 23:59:59</t>
   </si>
   <si>
     <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
@@ -992,6 +1004,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1004,13 +1019,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1325,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="2" customWidth="1"/>
@@ -1338,9 +1353,9 @@
     <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="15.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.25" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="20.8833333333333" style="4" customWidth="1"/>
+    <col min="12" max="12" width="21.175" style="4" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="5" customWidth="1"/>
     <col min="14" max="14" width="72.125" style="2" customWidth="1"/>
     <col min="15" max="15" width="9.375" style="2"/>
     <col min="16" max="16" width="19.875" style="2" customWidth="1"/>
@@ -1352,43 +1367,43 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -1396,113 +1411,113 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="G2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="9" t="s">
+      <c r="H2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="K3" s="9" t="s">
         <v>29</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="9"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H5" s="3">
         <v>1</v>
@@ -1513,17 +1528,17 @@
       <c r="J5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L5" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M5" s="4">
+      <c r="K5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="5">
         <v>99</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:14">
@@ -1531,37 +1546,37 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1</v>
-      </c>
-      <c r="J6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L6" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M6" s="4">
+      <c r="M6" s="5">
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:14">
@@ -1569,22 +1584,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H7" s="3">
         <v>1</v>
@@ -1595,17 +1610,17 @@
       <c r="J7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L7" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M7" s="4">
+      <c r="K7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="5">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1613,16 +1628,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H8" s="3">
         <v>1</v>
@@ -1630,17 +1645,17 @@
       <c r="J8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K8" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L8" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M8" s="4">
+      <c r="K8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="5">
         <v>1</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:14">
@@ -1648,16 +1663,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H9" s="3">
         <v>1</v>
@@ -1665,17 +1680,17 @@
       <c r="J9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L9" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="K9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="5">
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:14">
@@ -1683,17 +1698,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2">
         <v>6</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="3">
@@ -1703,17 +1718,17 @@
       <c r="J10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K10" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L10" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M10" s="4">
+      <c r="K10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="5">
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:14">
@@ -1721,16 +1736,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2">
         <v>7</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H11" s="3">
         <v>1</v>
@@ -1738,44 +1753,24 @@
       <c r="J11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K11" s="10">
-        <v>45931</v>
-      </c>
-      <c r="L11" s="10">
-        <v>45961.9999884259</v>
-      </c>
-      <c r="M11" s="4">
+      <c r="K11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M11" s="5">
         <v>3</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" spans="8:13">
       <c r="H13" s="3"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="15" spans="11:12">
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="11:12">
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="11:12">
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-    </row>
-    <row r="18" spans="11:12">
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="11:12">
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1796,37 +1791,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -109,36 +109,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-仅有 宣传弹窗图 才有按钮显示哟，其它 活动或功能图没有；
-配置时注意点
-参数：X坐标_Y坐标 </t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
   <si>
     <t>序号ID</t>
   </si>
@@ -158,7 +134,7 @@
     <t>活动或功能界面名称</t>
   </si>
   <si>
-    <t>按钮显示位置</t>
+    <t>打开界面需要导入的脚本</t>
   </si>
   <si>
     <t>每次登入弹出</t>
@@ -185,21 +161,18 @@
     <t>list&lt;list&lt;int&gt;{_}&gt;{;}</t>
   </si>
   <si>
-    <t>list&lt;string&gt;{_}</t>
+    <t>string</t>
   </si>
   <si>
     <t>list&lt;list&lt;string&gt;{_}&gt;{;}</t>
   </si>
   <si>
-    <t>list&lt;int&gt;{_}</t>
+    <t>list&lt;string&gt;{;}</t>
   </si>
   <si>
     <t>bool</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -209,13 +182,13 @@
     <t>serialNumber</t>
   </si>
   <si>
-    <t>windowUiName</t>
+    <t>imgName</t>
   </si>
   <si>
     <t>functionUiName</t>
   </si>
   <si>
-    <t>butPos</t>
+    <t>requires</t>
   </si>
   <si>
     <t>boolLogin</t>
@@ -242,7 +215,10 @@
     <t>首充</t>
   </si>
   <si>
-    <t>UICashCow_0</t>
+    <t>UIFirstRecharge_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIFirstRecharge/MVCHead</t>
   </si>
   <si>
     <t>2025/10/1 0:00:00</t>
@@ -260,7 +236,10 @@
     <t>每日奖金;成长基金;储钱罐</t>
   </si>
   <si>
-    <t>UICashCow_0;UICashCow_uiName;UICashCow_0</t>
+    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
   </si>
   <si>
     <t>2_9</t>
@@ -269,10 +248,13 @@
     <t>商城</t>
   </si>
   <si>
-    <t>UICashCow_uiName</t>
-  </si>
-  <si>
-    <t>258_125</t>
+    <t>lb_test1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
   </si>
   <si>
     <t>1_9;2_4;1_4;1_5;1_10</t>
@@ -281,7 +263,10 @@
     <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
   </si>
   <si>
-    <t>UICashCow_0;UICashCow_uiName;UICashCow_0;UICashCow_0;UICashCow_0</t>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
   </si>
   <si>
     <t>2_5;2_8;2_101;2_6</t>
@@ -290,7 +275,10 @@
     <t>推广分享;私人房间;我的赌场;VIP功能</t>
   </si>
   <si>
-    <t>UICashCow_0;UICashCow_uiName;UICashCow_0;UICashCow_0</t>
+    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
   </si>
   <si>
     <t>3_100100;3_200500;3_300100</t>
@@ -299,13 +287,13 @@
     <t>金矿大亨;百家乐;21点</t>
   </si>
   <si>
-    <t>UICashCow_0;UICashCow_0;UICashCow_0</t>
-  </si>
-  <si>
     <t>2_7</t>
   </si>
   <si>
     <t>公告</t>
+  </si>
+  <si>
+    <t>UINotice_0</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -991,7 +979,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1016,9 +1004,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1347,9 +1338,9 @@
     <col min="2" max="2" width="18.0833333333333" style="2" customWidth="1"/>
     <col min="3" max="3" width="40.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42" style="2" customWidth="1"/>
-    <col min="6" max="6" width="76.5" style="2" customWidth="1"/>
-    <col min="7" max="7" width="27" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.2416666666667" style="2" customWidth="1"/>
+    <col min="6" max="6" width="72.35" style="2" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="2" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="2" customWidth="1"/>
@@ -1385,7 +1376,7 @@
       <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
@@ -1397,13 +1388,13 @@
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="13" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -1414,20 +1405,20 @@
       <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -1439,53 +1430,53 @@
       <c r="J2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="10" t="s">
+      <c r="K2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
       <c r="A3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="M3" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="15" spans="1:13">
@@ -1495,43 +1486,46 @@
       <c r="D4" s="6"/>
       <c r="E4" s="7"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+      <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="H5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="10" t="b">
         <v>1</v>
       </c>
       <c r="J5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M5" s="5">
@@ -1557,19 +1551,22 @@
       <c r="F6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="G6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="b">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M6" s="5">
@@ -1584,36 +1581,36 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="3">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
+        <v>45</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="b">
         <v>1</v>
       </c>
       <c r="J7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M7" s="5">
@@ -1628,27 +1625,30 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2">
         <v>4</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="3">
+        <v>49</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="10" t="b">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M8" s="5">
@@ -1663,27 +1663,30 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2">
         <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="3">
+        <v>53</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="10" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="5">
@@ -1698,30 +1701,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2">
         <v>6</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3">
+      <c r="F10" s="2"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="10" t="b">
         <v>1</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M10" s="5">
@@ -1736,27 +1737,28 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2">
         <v>7</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="3">
+        <v>59</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="10" t="b">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="14" t="s">
         <v>36</v>
       </c>
       <c r="M11" s="5">
@@ -1766,7 +1768,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" spans="8:13">
+    <row r="13" s="2" customFormat="1" spans="7:13">
+      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1791,37 +1794,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="69">
   <si>
     <t>序号ID</t>
   </si>
@@ -224,69 +224,72 @@
     <t>2025/10/1 0:00:00</t>
   </si>
   <si>
+    <t>2035/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
+  </si>
+  <si>
+    <t>1_2;1_15;1_4</t>
+  </si>
+  <si>
+    <t>每日奖金;成长基金;储钱罐</t>
+  </si>
+  <si>
+    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>1_9;2_4;1_4;1_5;1_10</t>
+  </si>
+  <si>
+    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
+  </si>
+  <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
+  </si>
+  <si>
+    <t>2_5;2_8;2_101;2_6</t>
+  </si>
+  <si>
+    <t>推广分享;私人房间;我的赌场;VIP功能</t>
+  </si>
+  <si>
+    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
+  </si>
+  <si>
+    <t>2_9</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>lb_test1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
+  </si>
+  <si>
+    <t>3_100100;3_200500;3_300100</t>
+  </si>
+  <si>
+    <t>金矿大亨;百家乐;21点</t>
+  </si>
+  <si>
     <t>2025/10/31 23:59:59</t>
   </si>
   <si>
-    <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
-  </si>
-  <si>
-    <t>1_2;1_15;1_4</t>
-  </si>
-  <si>
-    <t>每日奖金;成长基金;储钱罐</t>
-  </si>
-  <si>
-    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
-  </si>
-  <si>
-    <t>2_9</t>
-  </si>
-  <si>
-    <t>商城</t>
-  </si>
-  <si>
-    <t>lb_test1.png</t>
-  </si>
-  <si>
-    <t>UIMall_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
-  </si>
-  <si>
-    <t>1_9;2_4;1_4;1_5;1_10</t>
-  </si>
-  <si>
-    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
-  </si>
-  <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
-  </si>
-  <si>
-    <t>2_5;2_8;2_101;2_6</t>
-  </si>
-  <si>
-    <t>推广分享;私人房间;我的赌场;VIP功能</t>
-  </si>
-  <si>
-    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
-  </si>
-  <si>
-    <t>3_100100;3_200500;3_300100</t>
-  </si>
-  <si>
-    <t>金矿大亨;百家乐;21点</t>
-  </si>
-  <si>
     <t>2_7</t>
   </si>
   <si>
@@ -315,6 +318,9 @@
   </si>
   <si>
     <t>充值商城：UIMall</t>
+  </si>
+  <si>
+    <t>不要删除，以下数据</t>
   </si>
 </sst>
 </file>
@@ -327,7 +333,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -345,6 +351,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -511,23 +523,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -848,55 +866,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -911,78 +926,84 @@
     <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -992,31 +1013,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1334,446 +1367,446 @@
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.0833333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="40.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.2416666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="72.35" style="2" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.8833333333333" style="4" customWidth="1"/>
-    <col min="12" max="12" width="21.175" style="4" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="72.125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="2"/>
-    <col min="16" max="16" width="19.875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9" style="2"/>
-    <col min="19" max="19" width="9.375" style="2"/>
-    <col min="20" max="20" width="23.25" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18.0833333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="40.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="23.2416666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="72.35" style="3" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="5" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="16.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="20.8833333333333" style="6" customWidth="1"/>
+    <col min="12" max="12" width="21.175" style="6" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="7" customWidth="1"/>
+    <col min="14" max="14" width="72.125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.375" style="3"/>
+    <col min="16" max="16" width="19.875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.75" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9" style="3"/>
+    <col min="19" max="19" width="9.375" style="3"/>
+    <col min="20" max="20" width="23.25" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="2" customFormat="1" ht="15" spans="1:14">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A2" s="6" t="s">
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:13">
+      <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A3" s="6" t="s">
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:13">
+      <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:13">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="13"/>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:13">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="15"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="10" t="b">
+      <c r="H5" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="10" t="b">
+      <c r="I5" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="b">
+      <c r="J5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="L5" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="7">
         <v>99</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:14">
-      <c r="A6" s="2">
+    <row r="6" s="3" customFormat="1" spans="1:14">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="10" t="b">
+      <c r="H6" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="10" t="b">
+      <c r="I6" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="b">
+      <c r="J6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="14" t="s">
+      <c r="L6" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="7">
+        <v>9</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="J7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="7">
+        <v>9</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:14">
-      <c r="A7" s="2">
+    <row r="8" s="4" customFormat="1" spans="1:14">
+      <c r="A8" s="4">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="M8" s="17">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="N8" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:14">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="7">
+        <v>9</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="1:14">
+      <c r="A10" s="4">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="17">
+        <v>1</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="1:14">
+      <c r="A11" s="4">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="4">
+        <v>7</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="17">
         <v>3</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="5">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="N11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="5">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:14">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" s="5">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" spans="1:14">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="2">
-        <v>6</v>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" s="5">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:14">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="2">
-        <v>7</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M11" s="5">
-        <v>3</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" spans="7:13">
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
+    <row r="13" s="3" customFormat="1" spans="7:13">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1786,46 +1819,290 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="31.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>66</v>
-      </c>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1">
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="1">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
   <si>
     <t>序号ID</t>
   </si>
@@ -248,79 +248,85 @@
     <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
   </si>
   <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UISignIn_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UISignIn/MVCHead</t>
+  </si>
+  <si>
+    <t>2_5;2_8;2_101;2_6</t>
+  </si>
+  <si>
+    <t>推广分享;私人房间;我的赌场;VIP功能</t>
+  </si>
+  <si>
+    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
+  </si>
+  <si>
+    <t>2_9</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
+    <t>lb_test1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
+  </si>
+  <si>
+    <t>3_100100;3_200500;3_300100</t>
+  </si>
+  <si>
+    <t>金矿大亨;百家乐;21点</t>
+  </si>
+  <si>
+    <t>2025/10/31 23:59:59</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>公告</t>
+  </si>
+  <si>
+    <t>UINotice_0</t>
+  </si>
+  <si>
+    <t>每日奖金(原月卡)：UIDailyBonus</t>
+  </si>
+  <si>
+    <t>摇钱树：UICashCow</t>
+  </si>
+  <si>
+    <t>储钱罐：UISavingPot</t>
+  </si>
+  <si>
+    <t>刮刮卡：UIScratchCards</t>
+  </si>
+  <si>
+    <t>创建房间：UICreatRoom</t>
+  </si>
+  <si>
+    <t>我的赌场：MyCasinoLoading</t>
+  </si>
+  <si>
+    <t>充值商城：UIMall</t>
+  </si>
+  <si>
+    <t>不要删除，以下数据</t>
+  </si>
+  <si>
     <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
   </si>
   <si>
     <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
-  </si>
-  <si>
-    <t>2_5;2_8;2_101;2_6</t>
-  </si>
-  <si>
-    <t>推广分享;私人房间;我的赌场;VIP功能</t>
-  </si>
-  <si>
-    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
-  </si>
-  <si>
-    <t>2_9</t>
-  </si>
-  <si>
-    <t>商城</t>
-  </si>
-  <si>
-    <t>lb_test1.png</t>
-  </si>
-  <si>
-    <t>UIMall_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
-  </si>
-  <si>
-    <t>3_100100;3_200500;3_300100</t>
-  </si>
-  <si>
-    <t>金矿大亨;百家乐;21点</t>
-  </si>
-  <si>
-    <t>2025/10/31 23:59:59</t>
-  </si>
-  <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>公告</t>
-  </si>
-  <si>
-    <t>UINotice_0</t>
-  </si>
-  <si>
-    <t>每日奖金(原月卡)：UIDailyBonus</t>
-  </si>
-  <si>
-    <t>摇钱树：UICashCow</t>
-  </si>
-  <si>
-    <t>储钱罐：UISavingPot</t>
-  </si>
-  <si>
-    <t>刮刮卡：UIScratchCards</t>
-  </si>
-  <si>
-    <t>创建房间：UICreatRoom</t>
-  </si>
-  <si>
-    <t>我的赌场：MyCasinoLoading</t>
-  </si>
-  <si>
-    <t>充值商城：UIMall</t>
-  </si>
-  <si>
-    <t>不要删除，以下数据</t>
   </si>
 </sst>
 </file>
@@ -523,12 +529,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1029,17 +1035,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1421,34 +1427,34 @@
       <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="12" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:13">
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:14">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="9" t="s">
@@ -1463,17 +1469,17 @@
       <c r="J2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:13">
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:14">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
@@ -1502,17 +1508,17 @@
       <c r="J3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:13">
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:14">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1523,9 +1529,9 @@
       <c r="H4" s="9"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="15"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="3">
@@ -1546,11 +1552,11 @@
       <c r="G5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="12" t="b">
+      <c r="H5" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="12" t="b">
-        <v>1</v>
+      <c r="I5" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="b">
         <v>1</v>
@@ -1587,11 +1593,11 @@
       <c r="G6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="12" t="b">
+      <c r="H6" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="12" t="b">
-        <v>1</v>
+      <c r="I6" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="b">
         <v>1</v>
@@ -1628,8 +1634,11 @@
       <c r="G7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="12" t="b">
+      <c r="H7" s="14" t="b">
         <v>1</v>
+      </c>
+      <c r="I7" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="b">
         <v>1</v>
@@ -1666,10 +1675,13 @@
       <c r="G8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="13" t="b">
+      <c r="H8" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="13" t="b">
+      <c r="I8" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="15" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="19" t="s">
@@ -1704,14 +1716,14 @@
       <c r="F9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="12" t="b">
+      <c r="H9" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="b">
-        <v>1</v>
+      <c r="I9" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="b">
         <v>1</v>
@@ -1745,11 +1757,13 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="13" t="b">
+      <c r="H10" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="13" t="b">
+      <c r="I10" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="15" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="19" t="s">
@@ -1782,10 +1796,13 @@
         <v>60</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="13" t="b">
+      <c r="H11" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="13" t="b">
+      <c r="I11" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="15" t="b">
         <v>0</v>
       </c>
       <c r="K11" s="19" t="s">
@@ -1801,7 +1818,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="7:13">
+    <row r="13" s="3" customFormat="1" spans="1:14">
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="K13" s="6"/>
@@ -1825,37 +1842,37 @@
     <col min="1" max="1" width="31.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1955,10 +1972,10 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="81">
   <si>
     <t>序号ID</t>
   </si>
@@ -230,6 +230,99 @@
     <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
   </si>
   <si>
+    <t>1_2;1_4;1_10</t>
+  </si>
+  <si>
+    <t>每日奖金;摇钱树;签到奖励</t>
+  </si>
+  <si>
+    <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UISignIn/MVCHead</t>
+  </si>
+  <si>
+    <t>1_9;2_4;1_5;1_4</t>
+  </si>
+  <si>
+    <t>官方派奖;积分大奖;刮刮乐;储钱罐</t>
+  </si>
+  <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UIScratchCards_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>2_5;2_8;2_101;2_6</t>
+  </si>
+  <si>
+    <t>推广分享;私人房间;我的赌场;VIP功能</t>
+  </si>
+  <si>
+    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
+  </si>
+  <si>
+    <t>2_9;1_15</t>
+  </si>
+  <si>
+    <t>商城;成长基金</t>
+  </si>
+  <si>
+    <t>lb_test1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0;UIGoldFund_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
+  </si>
+  <si>
+    <t>3_100100;3_200500;3_300100</t>
+  </si>
+  <si>
+    <t>金矿大亨;百家乐;21点</t>
+  </si>
+  <si>
+    <t>2025/10/31 23:59:59</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>公告</t>
+  </si>
+  <si>
+    <t>UINotice_0</t>
+  </si>
+  <si>
+    <t>每日奖金(原月卡)：UIDailyBonus</t>
+  </si>
+  <si>
+    <t>摇钱树：UICashCow</t>
+  </si>
+  <si>
+    <t>储钱罐：UISavingPot</t>
+  </si>
+  <si>
+    <t>刮刮卡：UIScratchCards</t>
+  </si>
+  <si>
+    <t>创建房间：UICreatRoom</t>
+  </si>
+  <si>
+    <t>我的赌场：MyCasinoLoading</t>
+  </si>
+  <si>
+    <t>充值商城：UIMall</t>
+  </si>
+  <si>
+    <t>不要删除，以下数据</t>
+  </si>
+  <si>
     <t>1_2;1_15;1_4</t>
   </si>
   <si>
@@ -248,22 +341,10 @@
     <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
   </si>
   <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UISignIn_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UISignIn/MVCHead</t>
-  </si>
-  <si>
-    <t>2_5;2_8;2_101;2_6</t>
-  </si>
-  <si>
-    <t>推广分享;私人房间;我的赌场;VIP功能</t>
-  </si>
-  <si>
-    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
   </si>
   <si>
     <t>2_9</t>
@@ -272,61 +353,10 @@
     <t>商城</t>
   </si>
   <si>
-    <t>lb_test1.png</t>
-  </si>
-  <si>
     <t>UIMall_0</t>
   </si>
   <si>
     <t>PlatformHall/UIActivities/UIMall/MVCHead</t>
-  </si>
-  <si>
-    <t>3_100100;3_200500;3_300100</t>
-  </si>
-  <si>
-    <t>金矿大亨;百家乐;21点</t>
-  </si>
-  <si>
-    <t>2025/10/31 23:59:59</t>
-  </si>
-  <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>公告</t>
-  </si>
-  <si>
-    <t>UINotice_0</t>
-  </si>
-  <si>
-    <t>每日奖金(原月卡)：UIDailyBonus</t>
-  </si>
-  <si>
-    <t>摇钱树：UICashCow</t>
-  </si>
-  <si>
-    <t>储钱罐：UISavingPot</t>
-  </si>
-  <si>
-    <t>刮刮卡：UIScratchCards</t>
-  </si>
-  <si>
-    <t>创建房间：UICreatRoom</t>
-  </si>
-  <si>
-    <t>我的赌场：MyCasinoLoading</t>
-  </si>
-  <si>
-    <t>充值商城：UIMall</t>
-  </si>
-  <si>
-    <t>不要删除，以下数据</t>
-  </si>
-  <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
   </si>
 </sst>
 </file>
@@ -356,7 +386,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -368,6 +397,7 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1003,7 +1033,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1022,10 +1052,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1044,12 +1074,21 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1373,27 +1412,27 @@
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18.0833333333333" style="3" customWidth="1"/>
-    <col min="3" max="3" width="40.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="23.2416666666667" style="3" customWidth="1"/>
-    <col min="6" max="6" width="72.35" style="3" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="5" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="71.3166666666667" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="23.2416666666667" style="5" customWidth="1"/>
+    <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
     <col min="11" max="11" width="20.8833333333333" style="6" customWidth="1"/>
     <col min="12" max="12" width="21.175" style="6" customWidth="1"/>
     <col min="13" max="13" width="12.875" style="7" customWidth="1"/>
-    <col min="14" max="14" width="72.125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="3"/>
-    <col min="16" max="16" width="19.875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.75" style="3" customWidth="1"/>
-    <col min="18" max="18" width="9" style="3"/>
-    <col min="19" max="19" width="9.375" style="3"/>
-    <col min="20" max="20" width="23.25" style="3" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="3"/>
+    <col min="14" max="14" width="72.125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="9.375" style="5"/>
+    <col min="16" max="16" width="19.875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="13.75" style="5" customWidth="1"/>
+    <col min="18" max="18" width="9" style="5"/>
+    <col min="19" max="19" width="9.375" style="5"/>
+    <col min="20" max="20" width="23.25" style="5" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="15" spans="1:14">
@@ -1534,22 +1573,22 @@
       <c r="M4" s="12"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="3">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="14" t="b">
@@ -1558,19 +1597,19 @@
       <c r="I5" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="b">
+      <c r="J5" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="18" t="s">
+      <c r="L5" s="20" t="s">
         <v>36</v>
       </c>
       <c r="M5" s="7">
-        <v>99</v>
-      </c>
-      <c r="N5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1590,7 +1629,7 @@
       <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>41</v>
       </c>
       <c r="H6" s="14" t="b">
@@ -1599,60 +1638,61 @@
       <c r="I6" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="b">
+      <c r="J6" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="7">
-        <v>9</v>
+      <c r="M6" s="17">
+        <v>1</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="3">
+    <row r="7" s="4" customFormat="1" spans="1:14">
+      <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="14" t="b">
-        <v>1</v>
+      <c r="H7" s="15" t="b">
+        <v>0</v>
       </c>
       <c r="I7" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="18" t="s">
+      <c r="J7" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="19">
         <v>9</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1684,36 +1724,36 @@
       <c r="J8" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="19" t="s">
+      <c r="L8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="17">
+      <c r="M8" s="19">
         <v>3</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:14">
-      <c r="A9" s="3">
+    <row r="9" s="5" customFormat="1" spans="1:14">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G9" s="14" t="s">
@@ -1725,19 +1765,19 @@
       <c r="I9" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="b">
+      <c r="J9" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="20" t="s">
         <v>36</v>
       </c>
       <c r="M9" s="7">
-        <v>9</v>
-      </c>
-      <c r="N9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N9" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1766,13 +1806,13 @@
       <c r="J10" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="19">
         <v>1</v>
       </c>
       <c r="N10" s="4" t="s">
@@ -1805,22 +1845,22 @@
       <c r="J11" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="19" t="s">
+      <c r="L11" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="19">
         <v>3</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="3" customFormat="1" spans="1:14">
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+    <row r="13" s="5" customFormat="1" spans="1:14">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="7"/>
@@ -1932,20 +1972,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -1962,20 +2002,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2022,10 +2062,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -2034,10 +2074,10 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -114,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="82">
   <si>
     <t>序号ID</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>UINotice_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UINotice/MVCHead</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -1835,7 +1838,9 @@
       <c r="F11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="H11" s="15" t="b">
         <v>0</v>
       </c>
@@ -1884,42 +1889,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1972,20 +1977,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2002,20 +2007,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2062,10 +2067,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
@@ -2074,10 +2079,10 @@
         <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,8 @@
 宣传图名称_页签名称; 
 页签名称通常为0，除非宣传图上有页签功能
 注：页签名称为0时，表示打开指定界面即可；不要求精准
-</t>
+弹窗宣传图资源  是从资源服实时下载的；
+tanchuang_res/资源名称.png(或gif)</t>
         </r>
       </text>
     </comment>
@@ -114,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
   <si>
     <t>序号ID</t>
   </si>
@@ -161,18 +162,18 @@
     <t>list&lt;list&lt;int&gt;{_}&gt;{;}</t>
   </si>
   <si>
+    <t>list&lt;string&gt;{;}</t>
+  </si>
+  <si>
+    <t>list&lt;list&lt;string&gt;{_}&gt;{;}</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>list&lt;list&lt;string&gt;{_}&gt;{;}</t>
-  </si>
-  <si>
-    <t>list&lt;string&gt;{;}</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -236,6 +237,9 @@
     <t>每日奖金;摇钱树;签到奖励</t>
   </si>
   <si>
+    <t>tanchuang_res/tc_mrjj_1.png;0;0</t>
+  </si>
+  <si>
     <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
   </si>
   <si>
@@ -272,88 +276,91 @@
     <t>商城;成长基金</t>
   </si>
   <si>
+    <t>tanchuang_res/tc_sc_1.png;tanchuang_res/tc_czjj_1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0;UIGoldFund_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
+  </si>
+  <si>
+    <t>3_100100;3_200500;3_300100</t>
+  </si>
+  <si>
+    <t>金矿大亨;百家乐;21点</t>
+  </si>
+  <si>
+    <t>2025/10/31 23:59:59</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>公告</t>
+  </si>
+  <si>
+    <t>UINotice_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UINotice/MVCHead</t>
+  </si>
+  <si>
+    <t>每日奖金(原月卡)：UIDailyBonus</t>
+  </si>
+  <si>
+    <t>摇钱树：UICashCow</t>
+  </si>
+  <si>
+    <t>储钱罐：UISavingPot</t>
+  </si>
+  <si>
+    <t>刮刮卡：UIScratchCards</t>
+  </si>
+  <si>
+    <t>创建房间：UICreatRoom</t>
+  </si>
+  <si>
+    <t>我的赌场：MyCasinoLoading</t>
+  </si>
+  <si>
+    <t>充值商城：UIMall</t>
+  </si>
+  <si>
+    <t>不要删除，以下数据</t>
+  </si>
+  <si>
+    <t>1_2;1_15;1_4</t>
+  </si>
+  <si>
+    <t>每日奖金;成长基金;储钱罐</t>
+  </si>
+  <si>
+    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>1_9;2_4;1_4;1_5;1_10</t>
+  </si>
+  <si>
+    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
+  </si>
+  <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
+  </si>
+  <si>
+    <t>2_9</t>
+  </si>
+  <si>
+    <t>商城</t>
+  </si>
+  <si>
     <t>lb_test1.png</t>
-  </si>
-  <si>
-    <t>UIMall_0;UIGoldFund_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
-  </si>
-  <si>
-    <t>3_100100;3_200500;3_300100</t>
-  </si>
-  <si>
-    <t>金矿大亨;百家乐;21点</t>
-  </si>
-  <si>
-    <t>2025/10/31 23:59:59</t>
-  </si>
-  <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>公告</t>
-  </si>
-  <si>
-    <t>UINotice_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UINotice/MVCHead</t>
-  </si>
-  <si>
-    <t>每日奖金(原月卡)：UIDailyBonus</t>
-  </si>
-  <si>
-    <t>摇钱树：UICashCow</t>
-  </si>
-  <si>
-    <t>储钱罐：UISavingPot</t>
-  </si>
-  <si>
-    <t>刮刮卡：UIScratchCards</t>
-  </si>
-  <si>
-    <t>创建房间：UICreatRoom</t>
-  </si>
-  <si>
-    <t>我的赌场：MyCasinoLoading</t>
-  </si>
-  <si>
-    <t>充值商城：UIMall</t>
-  </si>
-  <si>
-    <t>不要删除，以下数据</t>
-  </si>
-  <si>
-    <t>1_2;1_15;1_4</t>
-  </si>
-  <si>
-    <t>每日奖金;成长基金;储钱罐</t>
-  </si>
-  <si>
-    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
-  </si>
-  <si>
-    <t>1_9;2_4;1_4;1_5;1_10</t>
-  </si>
-  <si>
-    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
-  </si>
-  <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
-  </si>
-  <si>
-    <t>2_9</t>
-  </si>
-  <si>
-    <t>商城</t>
   </si>
   <si>
     <t>UIMall_0</t>
@@ -1036,7 +1043,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1055,6 +1062,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1064,10 +1074,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1079,11 +1092,17 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
@@ -1417,17 +1436,17 @@
   <cols>
     <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
     <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="71.3166666666667" style="5" customWidth="1"/>
+    <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
     <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="23.2416666666667" style="5" customWidth="1"/>
+    <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
     <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
     <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
     <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20.8833333333333" style="6" customWidth="1"/>
-    <col min="12" max="12" width="21.175" style="6" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
+    <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="8" customWidth="1"/>
     <col min="14" max="14" width="72.125" style="5" customWidth="1"/>
     <col min="15" max="15" width="9.375" style="5"/>
     <col min="16" max="16" width="19.875" style="5" customWidth="1"/>
@@ -1439,43 +1458,43 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
@@ -1483,97 +1502,97 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="L2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="12"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="14"/>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="5">
@@ -1588,28 +1607,29 @@
       <c r="D5" s="5">
         <v>1</v>
       </c>
+      <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="14" t="b">
+      <c r="H5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="15" t="b">
+      <c r="I5" s="17" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="20" t="s">
+      <c r="L5" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="8">
         <v>3</v>
       </c>
       <c r="N5" s="5" t="s">
@@ -1629,28 +1649,31 @@
       <c r="D6" s="3">
         <v>2</v>
       </c>
+      <c r="E6" s="18" t="s">
+        <v>40</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="14" t="b">
+        <v>42</v>
+      </c>
+      <c r="H6" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="15" t="b">
+      <c r="I6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="14" t="b">
+      <c r="J6" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="17">
+      <c r="M6" s="20">
         <v>1</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1662,37 +1685,37 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="15" t="b">
+        <v>46</v>
+      </c>
+      <c r="H7" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="15" t="b">
+      <c r="I7" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="15" t="b">
+      <c r="J7" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="22" t="s">
+      <c r="K7" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="L7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="23">
         <v>9</v>
       </c>
       <c r="N7" s="4" t="s">
@@ -1704,36 +1727,37 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
+      <c r="E8" s="21"/>
       <c r="F8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="15" t="b">
+        <v>50</v>
+      </c>
+      <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="15" t="b">
+      <c r="I8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="15" t="b">
+      <c r="J8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="22" t="s">
+      <c r="L8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="19">
+      <c r="M8" s="23">
         <v>3</v>
       </c>
       <c r="N8" s="4" t="s">
@@ -1745,39 +1769,39 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>52</v>
+      <c r="E9" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="14" t="b">
+      <c r="G9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="15" t="b">
+      <c r="I9" s="17" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="20" t="s">
+      <c r="L9" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="8">
         <v>2</v>
       </c>
       <c r="N9" s="5" t="s">
@@ -1789,33 +1813,33 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="4">
         <v>6</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="21"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="15" t="b">
+      <c r="H10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="15" t="b">
+      <c r="I10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="15" t="b">
+      <c r="J10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="M10" s="19">
+      <c r="L10" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="23">
         <v>1</v>
       </c>
       <c r="N10" s="4" t="s">
@@ -1827,36 +1851,37 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" s="4">
         <v>7</v>
       </c>
+      <c r="E11" s="21"/>
       <c r="F11" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="15" t="b">
+        <v>62</v>
+      </c>
+      <c r="H11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="15" t="b">
+      <c r="I11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="15" t="b">
+      <c r="J11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="22" t="s">
+      <c r="K11" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11" s="19">
+      <c r="L11" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="23">
         <v>3</v>
       </c>
       <c r="N11" s="4" t="s">
@@ -1864,11 +1889,12 @@
       </c>
     </row>
     <row r="13" s="5" customFormat="1" spans="1:14">
+      <c r="E13" s="6"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1889,42 +1915,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1977,20 +2003,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2007,20 +2033,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2037,20 +2063,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2067,22 +2093,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2099,10 +2125,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2125,17 +2151,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -54,6 +54,7 @@
 1. 活动：ActivityConfig.xlsx  读取该表中的活动&lt;type&gt;字段值
 2. 功能：GameFunction.xlsx 读取该表中的&lt;ID&gt;字段值
 3. 游戏ID：warehouse.xlsx 读取该表中的&lt;gameID&gt;字段值
+4. 是功能同时也是活动  配置warehouse.xlsx 读取该表中的&lt;ID&gt;字段值
 描述：配置多个功能弹窗时，随机一个弹出；仅配置一个 则必弹；
 参数例子：
    1_11       //类型ID_对应功能ID
@@ -115,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
   <si>
     <t>序号ID</t>
   </si>
@@ -210,148 +211,154 @@
     <t>count</t>
   </si>
   <si>
+    <t>4_11</t>
+  </si>
+  <si>
+    <t>首充</t>
+  </si>
+  <si>
+    <t>UIFirstRecharge_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIFirstRecharge/MVCHead</t>
+  </si>
+  <si>
+    <t>2025/10/1 0:00:00</t>
+  </si>
+  <si>
+    <t>2035/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
+  </si>
+  <si>
+    <t>4_2;4_4;4_10</t>
+  </si>
+  <si>
+    <t>每日奖金;摇钱树;签到奖励</t>
+  </si>
+  <si>
+    <t>tanchuang_res/tc_mrjj_1.png;0;0</t>
+  </si>
+  <si>
+    <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UISignIn/MVCHead</t>
+  </si>
+  <si>
+    <t>4_9;2_4;4_5;4_4</t>
+  </si>
+  <si>
+    <t>官方派奖;积分大奖;刮刮乐;储钱罐</t>
+  </si>
+  <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UIScratchCards_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>4_5;2_8;2_101;2_6</t>
+  </si>
+  <si>
+    <t>推广分享;私人房间;我的赌场;VIP功能</t>
+  </si>
+  <si>
+    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
+  </si>
+  <si>
+    <t>2_9;4_15</t>
+  </si>
+  <si>
+    <t>商城;成长基金</t>
+  </si>
+  <si>
+    <t>tanchuang_res/tc_sc_1.png;tanchuang_res/tc_czjj_1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0;UIGoldFund_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
+  </si>
+  <si>
+    <t>3_100100;3_200500;3_300100</t>
+  </si>
+  <si>
+    <t>金矿大亨;百家乐;21点</t>
+  </si>
+  <si>
+    <t>2025/10/31 23:59:59</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>公告</t>
+  </si>
+  <si>
+    <t>UINotice_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UINotice/MVCHead</t>
+  </si>
+  <si>
+    <t>每日奖金(原月卡)：UIDailyBonus</t>
+  </si>
+  <si>
+    <t>摇钱树：UICashCow</t>
+  </si>
+  <si>
+    <t>储钱罐：UISavingPot</t>
+  </si>
+  <si>
+    <t>刮刮卡：UIScratchCards</t>
+  </si>
+  <si>
+    <t>创建房间：UICreatRoom</t>
+  </si>
+  <si>
+    <t>我的赌场：MyCasinoLoading</t>
+  </si>
+  <si>
+    <t>充值商城：UIMall</t>
+  </si>
+  <si>
+    <t>不要删除，以下数据</t>
+  </si>
+  <si>
     <t>1_11</t>
   </si>
   <si>
-    <t>首充</t>
-  </si>
-  <si>
-    <t>UIFirstRecharge_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIFirstRecharge/MVCHead</t>
-  </si>
-  <si>
-    <t>2025/10/1 0:00:00</t>
-  </si>
-  <si>
-    <t>2035/12/31 23:59:59</t>
-  </si>
-  <si>
-    <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
-  </si>
-  <si>
-    <t>1_2;1_4;1_10</t>
-  </si>
-  <si>
-    <t>每日奖金;摇钱树;签到奖励</t>
-  </si>
-  <si>
-    <t>tanchuang_res/tc_mrjj_1.png;0;0</t>
-  </si>
-  <si>
-    <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UISignIn/MVCHead</t>
-  </si>
-  <si>
-    <t>1_9;2_4;1_5;1_4</t>
-  </si>
-  <si>
-    <t>官方派奖;积分大奖;刮刮乐;储钱罐</t>
-  </si>
-  <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UIScratchCards_0;UISavingPot_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+    <t>1_2;1_15;1_4</t>
+  </si>
+  <si>
+    <t>每日奖金;成长基金;储钱罐</t>
+  </si>
+  <si>
+    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>1_9;2_4;1_4;1_5;1_10</t>
+  </si>
+  <si>
+    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
+  </si>
+  <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
   </si>
   <si>
     <t>2_5;2_8;2_101;2_6</t>
-  </si>
-  <si>
-    <t>推广分享;私人房间;我的赌场;VIP功能</t>
-  </si>
-  <si>
-    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
-  </si>
-  <si>
-    <t>2_9;1_15</t>
-  </si>
-  <si>
-    <t>商城;成长基金</t>
-  </si>
-  <si>
-    <t>tanchuang_res/tc_sc_1.png;tanchuang_res/tc_czjj_1.png</t>
-  </si>
-  <si>
-    <t>UIMall_0;UIGoldFund_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
-  </si>
-  <si>
-    <t>3_100100;3_200500;3_300100</t>
-  </si>
-  <si>
-    <t>金矿大亨;百家乐;21点</t>
-  </si>
-  <si>
-    <t>2025/10/31 23:59:59</t>
-  </si>
-  <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>公告</t>
-  </si>
-  <si>
-    <t>UINotice_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UINotice/MVCHead</t>
-  </si>
-  <si>
-    <t>每日奖金(原月卡)：UIDailyBonus</t>
-  </si>
-  <si>
-    <t>摇钱树：UICashCow</t>
-  </si>
-  <si>
-    <t>储钱罐：UISavingPot</t>
-  </si>
-  <si>
-    <t>刮刮卡：UIScratchCards</t>
-  </si>
-  <si>
-    <t>创建房间：UICreatRoom</t>
-  </si>
-  <si>
-    <t>我的赌场：MyCasinoLoading</t>
-  </si>
-  <si>
-    <t>充值商城：UIMall</t>
-  </si>
-  <si>
-    <t>不要删除，以下数据</t>
-  </si>
-  <si>
-    <t>1_2;1_15;1_4</t>
-  </si>
-  <si>
-    <t>每日奖金;成长基金;储钱罐</t>
-  </si>
-  <si>
-    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
-  </si>
-  <si>
-    <t>1_9;2_4;1_4;1_5;1_10</t>
-  </si>
-  <si>
-    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
-  </si>
-  <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
   </si>
   <si>
     <t>2_9</t>
@@ -1607,7 +1614,6 @@
       <c r="D5" s="5">
         <v>1</v>
       </c>
-      <c r="E5" s="6"/>
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
@@ -1973,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2003,20 +2009,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2033,20 +2039,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2063,7 +2069,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>48</v>
@@ -2093,22 +2099,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -211,7 +211,7 @@
     <t>count</t>
   </si>
   <si>
-    <t>4_11</t>
+    <t>4_106</t>
   </si>
   <si>
     <t>首充</t>
@@ -232,7 +232,7 @@
     <t>达到解锁条件，在弹窗时间范围、活动\功能开启中且没有完成活动条件时弹出</t>
   </si>
   <si>
-    <t>4_2;4_4;4_10</t>
+    <t>4_102;4_2;4_108</t>
   </si>
   <si>
     <t>每日奖金;摇钱树;签到奖励</t>
@@ -247,7 +247,7 @@
     <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UISignIn/MVCHead</t>
   </si>
   <si>
-    <t>4_9;2_4;4_5;4_4</t>
+    <t>4_3;2_4;4_103;4_104</t>
   </si>
   <si>
     <t>官方派奖;积分大奖;刮刮乐;储钱罐</t>
@@ -271,7 +271,7 @@
     <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
   </si>
   <si>
-    <t>2_9;4_15</t>
+    <t>2_9;4_107</t>
   </si>
   <si>
     <t>商城;成长基金</t>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="88">
   <si>
     <t>序号ID</t>
   </si>
@@ -265,100 +265,106 @@
     <t>推广分享;私人房间;我的赌场;VIP功能</t>
   </si>
   <si>
+    <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVIPNew_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVIPNew/MVCHead</t>
+  </si>
+  <si>
+    <t>2_9;4_107</t>
+  </si>
+  <si>
+    <t>商城;成长基金</t>
+  </si>
+  <si>
+    <t>tanchuang_res/tc_sc_1.png;tanchuang_res/tc_czjj_1.png</t>
+  </si>
+  <si>
+    <t>UIMall_0;UIGoldFund_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
+  </si>
+  <si>
+    <t>3_100100;3_200500;3_300100</t>
+  </si>
+  <si>
+    <t>金矿大亨;百家乐;21点</t>
+  </si>
+  <si>
+    <t>2025/10/31 23:59:59</t>
+  </si>
+  <si>
+    <t>2_7</t>
+  </si>
+  <si>
+    <t>公告</t>
+  </si>
+  <si>
+    <t>UINotice_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UINotice/MVCHead</t>
+  </si>
+  <si>
+    <t>每日奖金(原月卡)：UIDailyBonus</t>
+  </si>
+  <si>
+    <t>摇钱树：UICashCow</t>
+  </si>
+  <si>
+    <t>储钱罐：UISavingPot</t>
+  </si>
+  <si>
+    <t>刮刮卡：UIScratchCards</t>
+  </si>
+  <si>
+    <t>创建房间：UICreatRoom</t>
+  </si>
+  <si>
+    <t>我的赌场：MyCasinoLoading</t>
+  </si>
+  <si>
+    <t>充值商城：UIMall</t>
+  </si>
+  <si>
+    <t>不要删除，以下数据</t>
+  </si>
+  <si>
+    <t>1_11</t>
+  </si>
+  <si>
+    <t>1_2;1_15;1_4</t>
+  </si>
+  <si>
+    <t>每日奖金;成长基金;储钱罐</t>
+  </si>
+  <si>
+    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
+  </si>
+  <si>
+    <t>1_9;2_4;1_4;1_5;1_10</t>
+  </si>
+  <si>
+    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
+  </si>
+  <si>
+    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
+  </si>
+  <si>
+    <t>2_5;2_8;2_101;2_6</t>
+  </si>
+  <si>
     <t>UISharePromote_0;UICreatRoom_0;MyCasinoLoading_0;UIVip_0</t>
   </si>
   <si>
     <t>PlatformHall/UIActivities/UISharePromote/MVCHead;PlatformHall/UICreatRoom/MVCHead;PlatformHall/MyCasino/MVCHead;PlatformHall/UIVip/MVCHead</t>
-  </si>
-  <si>
-    <t>2_9;4_107</t>
-  </si>
-  <si>
-    <t>商城;成长基金</t>
-  </si>
-  <si>
-    <t>tanchuang_res/tc_sc_1.png;tanchuang_res/tc_czjj_1.png</t>
-  </si>
-  <si>
-    <t>UIMall_0;UIGoldFund_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIMall/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead</t>
-  </si>
-  <si>
-    <t>3_100100;3_200500;3_300100</t>
-  </si>
-  <si>
-    <t>金矿大亨;百家乐;21点</t>
-  </si>
-  <si>
-    <t>2025/10/31 23:59:59</t>
-  </si>
-  <si>
-    <t>2_7</t>
-  </si>
-  <si>
-    <t>公告</t>
-  </si>
-  <si>
-    <t>UINotice_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UINotice/MVCHead</t>
-  </si>
-  <si>
-    <t>每日奖金(原月卡)：UIDailyBonus</t>
-  </si>
-  <si>
-    <t>摇钱树：UICashCow</t>
-  </si>
-  <si>
-    <t>储钱罐：UISavingPot</t>
-  </si>
-  <si>
-    <t>刮刮卡：UIScratchCards</t>
-  </si>
-  <si>
-    <t>创建房间：UICreatRoom</t>
-  </si>
-  <si>
-    <t>我的赌场：MyCasinoLoading</t>
-  </si>
-  <si>
-    <t>充值商城：UIMall</t>
-  </si>
-  <si>
-    <t>不要删除，以下数据</t>
-  </si>
-  <si>
-    <t>1_11</t>
-  </si>
-  <si>
-    <t>1_2;1_15;1_4</t>
-  </si>
-  <si>
-    <t>每日奖金;成长基金;储钱罐</t>
-  </si>
-  <si>
-    <t>UIDailyBonus_0;UIGoldFund_0;UISavingPot_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/UIDailyBonus/MVCHead;PlatformHall/UIActivities/UIGoldFund/MVCHead;PlatformHall/UIActivities/UISavingPot/MVCHead</t>
-  </si>
-  <si>
-    <t>1_9;2_4;1_4;1_5;1_10</t>
-  </si>
-  <si>
-    <t>官方派奖;积分大奖;摇钱树;刮刮乐;签到奖励</t>
-  </si>
-  <si>
-    <t>OfficialPrize_0;UIIntegralBigPrize_0;UICashCow_0;UIScratchCards_0;UIDailyBonus_0</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIActivities/OfficialPrize/MVCHead;PlatformHall/UIActivities/UIIntegralBigPrize/MVCHead;PlatformHall/UIActivities/UICashCow/MVCHead;PlatformHall/UIActivities/UIScratchCards/MVCHead;PlatformHall/UIActivities/UIDailyBonus/MVCHead</t>
-  </si>
-  <si>
-    <t>2_5;2_8;2_101;2_6</t>
   </si>
   <si>
     <t>2_9</t>
@@ -2079,10 +2085,10 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2099,22 +2105,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 宣传图名称_页签名称; 
 页签名称通常为0，除非宣传图上有页签功能
 注：页签名称为0时，表示打开指定界面即可；不要求精准
-弹窗宣传图资源  是从资源服实时下载的；
+弹窗宣传图资源  是从资源服实时下载的；后台没有配置表
 tanchuang_res/资源名称.png(或gif)</t>
         </r>
       </text>
@@ -238,7 +238,7 @@
     <t>每日奖金;摇钱树;签到奖励</t>
   </si>
   <si>
-    <t>tanchuang_res/tc_mrjj_1.png;0;0</t>
+    <t>tanchuang_res/%s/tc_mrjj_1.png;0;0</t>
   </si>
   <si>
     <t>UIDailyBonus_0;UICashCow_0;UISignIn_0</t>
@@ -277,7 +277,7 @@
     <t>商城;成长基金</t>
   </si>
   <si>
-    <t>tanchuang_res/tc_sc_1.png;tanchuang_res/tc_czjj_1.png</t>
+    <t>tanchuang_res/%s/tc_sc_1.png;tanchuang_res/%s/tc_czjj_1.png</t>
   </si>
   <si>
     <t>UIMall_0;UIGoldFund_0</t>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
   <si>
     <t>序号ID</t>
   </si>
@@ -305,6 +305,12 @@
   </si>
   <si>
     <t>PlatformHall/UINotice/MVCHead</t>
+  </si>
+  <si>
+    <t>19_121</t>
+  </si>
+  <si>
+    <t>买一送七</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -582,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1810,8 +1816,8 @@
       <c r="K9" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="24" t="s">
-        <v>36</v>
+      <c r="L9" s="26" t="s">
+        <v>35</v>
       </c>
       <c r="M9" s="8">
         <v>2</v>
@@ -1897,6 +1903,41 @@
         <v>3</v>
       </c>
       <c r="N11" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8</v>
+      </c>
+      <c r="H12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M12" s="23">
+        <v>1</v>
+      </c>
+      <c r="N12" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1927,42 +1968,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1985,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2015,20 +2056,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2045,20 +2086,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2075,7 +2116,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>48</v>
@@ -2085,10 +2126,10 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2105,22 +2146,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -588,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1109,7 +1109,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1129,6 +1128,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1633,13 +1633,13 @@
         <v>34</v>
       </c>
       <c r="H5" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>35</v>
@@ -1667,7 +1667,7 @@
       <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1677,13 +1677,13 @@
         <v>42</v>
       </c>
       <c r="H6" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="b">
         <v>0</v>
       </c>
       <c r="J6" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="25" t="s">
         <v>35</v>
@@ -1691,7 +1691,7 @@
       <c r="L6" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="19">
         <v>1</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1711,20 +1711,20 @@
       <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="17" t="b">
+      <c r="H7" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16" t="b">
         <v>0</v>
       </c>
       <c r="K7" s="26" t="s">
@@ -1733,7 +1733,7 @@
       <c r="L7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="22">
         <v>9</v>
       </c>
       <c r="N7" s="4" t="s">
@@ -1753,20 +1753,20 @@
       <c r="D8" s="4">
         <v>4</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="17" t="b">
+      <c r="H8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="16" t="b">
         <v>0</v>
       </c>
       <c r="K8" s="26" t="s">
@@ -1775,7 +1775,7 @@
       <c r="L8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="22">
         <v>3</v>
       </c>
       <c r="N8" s="4" t="s">
@@ -1801,17 +1801,17 @@
       <c r="F9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="23" t="s">
         <v>55</v>
       </c>
       <c r="H9" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16" t="b">
+        <v>0</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>35</v>
@@ -1839,16 +1839,16 @@
       <c r="D10" s="4">
         <v>6</v>
       </c>
-      <c r="E10" s="21"/>
+      <c r="E10" s="20"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="17" t="b">
+      <c r="H10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16" t="b">
         <v>0</v>
       </c>
       <c r="K10" s="26" t="s">
@@ -1857,7 +1857,7 @@
       <c r="L10" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="22">
         <v>1</v>
       </c>
       <c r="N10" s="4" t="s">
@@ -1877,20 +1877,20 @@
       <c r="D11" s="4">
         <v>7</v>
       </c>
-      <c r="E11" s="21"/>
+      <c r="E11" s="20"/>
       <c r="F11" s="4" t="s">
         <v>61</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="17" t="b">
+      <c r="H11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16" t="b">
         <v>0</v>
       </c>
       <c r="K11" s="26" t="s">
@@ -1899,7 +1899,7 @@
       <c r="L11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="22">
         <v>3</v>
       </c>
       <c r="N11" s="4" t="s">
@@ -1919,13 +1919,13 @@
       <c r="D12" s="5">
         <v>8</v>
       </c>
-      <c r="H12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17" t="b">
+      <c r="H12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="16" t="b">
         <v>0</v>
       </c>
       <c r="K12" s="26" t="s">
@@ -1934,7 +1934,7 @@
       <c r="L12" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="22">
         <v>1</v>
       </c>
       <c r="N12" s="4" t="s">

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="94">
   <si>
     <t>序号ID</t>
   </si>
@@ -311,6 +311,18 @@
   </si>
   <si>
     <t>买一送七</t>
+  </si>
+  <si>
+    <t>1_21</t>
+  </si>
+  <si>
+    <t>没绑定手机时弹窗</t>
+  </si>
+  <si>
+    <t>UIUserInfo_0|-1|btn_phone</t>
+  </si>
+  <si>
+    <t>PlatformHall/UIUserInfo/MVCHead</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -415,12 +427,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1110,6 +1122,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1128,7 +1141,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1459,8 +1471,8 @@
     <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
     <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
     <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
@@ -1629,17 +1641,17 @@
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="16" t="b">
-        <v>0</v>
-      </c>
       <c r="J5" s="16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>35</v>
@@ -1667,7 +1679,7 @@
       <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1676,13 +1688,13 @@
       <c r="G6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="16" t="b">
+      <c r="H6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="16" t="b">
+      <c r="I6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="16" t="b">
+      <c r="J6" s="17" t="b">
         <v>0</v>
       </c>
       <c r="K6" s="25" t="s">
@@ -1691,7 +1703,7 @@
       <c r="L6" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="20">
         <v>1</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1711,7 +1723,7 @@
       <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="4" t="s">
         <v>45</v>
       </c>
@@ -1719,13 +1731,13 @@
         <v>46</v>
       </c>
       <c r="H7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="16" t="b">
-        <v>0</v>
-      </c>
       <c r="J7" s="16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>35</v>
@@ -1733,221 +1745,257 @@
       <c r="L7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="22">
-        <v>9</v>
+      <c r="M7" s="23">
+        <v>5</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" spans="1:14">
-      <c r="A8" s="4">
+    <row r="8" s="3" customFormat="1" spans="1:14">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>4</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="18"/>
+      <c r="F8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="16" t="b">
+      <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="16" t="b">
+      <c r="I8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="16" t="b">
+      <c r="J8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="26" t="s">
+      <c r="L8" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="22">
+      <c r="M8" s="20">
         <v>3</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="1" spans="1:14">
-      <c r="A9" s="5">
+    <row r="9" s="3" customFormat="1" spans="1:14">
+      <c r="A9" s="3">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>5</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="16" t="b">
+      <c r="H9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="16" t="b">
+      <c r="I9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="16" t="b">
+      <c r="J9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="26" t="s">
+      <c r="L9" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="20">
         <v>2</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N9" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" spans="1:14">
-      <c r="A10" s="4">
+    <row r="10" s="3" customFormat="1" spans="1:14">
+      <c r="A10" s="3">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>6</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="16" t="b">
+      <c r="E10" s="18"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="16" t="b">
+      <c r="I10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="16" t="b">
+      <c r="J10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="26" t="s">
+      <c r="K10" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="26" t="s">
+      <c r="L10" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="20">
         <v>1</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" spans="1:14">
-      <c r="A11" s="4">
+    <row r="11" s="3" customFormat="1" spans="1:14">
+      <c r="A11" s="3">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>7</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="16" t="b">
+      <c r="H11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="16" t="b">
+      <c r="I11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="16" t="b">
+      <c r="J11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="26" t="s">
+      <c r="L11" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="22">
+      <c r="M11" s="20">
         <v>3</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4">
+    <row r="12" s="3" customFormat="1" spans="1:14">
+      <c r="A12" s="3">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>8</v>
       </c>
-      <c r="H12" s="16" t="b">
+      <c r="E12" s="18"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="16" t="b">
+      <c r="I12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="16" t="b">
+      <c r="J12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="26" t="s">
+      <c r="K12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="26" t="s">
+      <c r="L12" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="22">
+      <c r="M12" s="20">
         <v>1</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="5" customFormat="1" spans="1:14">
-      <c r="E13" s="6"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="8"/>
+    <row r="13" s="4" customFormat="1" spans="1:14">
+      <c r="A13" s="4">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="4">
+        <v>9</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="23">
+        <v>999</v>
+      </c>
+      <c r="N13" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1968,42 +2016,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2026,7 +2074,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2056,20 +2104,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2086,20 +2134,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2116,7 +2164,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>48</v>
@@ -2126,10 +2174,10 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2146,22 +2194,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
   <si>
     <t>序号ID</t>
   </si>
@@ -311,18 +311,6 @@
   </si>
   <si>
     <t>买一送七</t>
-  </si>
-  <si>
-    <t>1_21</t>
-  </si>
-  <si>
-    <t>没绑定手机时弹窗</t>
-  </si>
-  <si>
-    <t>UIUserInfo_0|-1|btn_phone</t>
-  </si>
-  <si>
-    <t>PlatformHall/UIUserInfo/MVCHead</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -600,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1957,45 +1945,14 @@
       </c>
     </row>
     <row r="13" s="4" customFormat="1" spans="1:14">
-      <c r="A13" s="4">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="4">
-        <v>9</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M13" s="23">
-        <v>999</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2016,42 +1973,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2074,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2104,20 +2061,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2134,20 +2091,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2164,7 +2121,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>48</v>
@@ -2174,10 +2131,10 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2194,22 +2151,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -415,12 +415,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -588,12 +588,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1110,7 +1110,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1129,6 +1128,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1459,8 +1459,8 @@
     <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
     <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
     <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
@@ -1629,17 +1629,17 @@
       <c r="F5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="16" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>35</v>
@@ -1667,7 +1667,7 @@
       <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1676,13 +1676,13 @@
       <c r="G6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="17" t="b">
+      <c r="H6" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="16" t="b">
         <v>0</v>
       </c>
       <c r="K6" s="25" t="s">
@@ -1691,7 +1691,7 @@
       <c r="L6" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="19">
         <v>1</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1711,7 +1711,7 @@
       <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="21"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="4" t="s">
         <v>45</v>
       </c>
@@ -1719,13 +1719,13 @@
         <v>46</v>
       </c>
       <c r="H7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="b">
         <v>0</v>
       </c>
       <c r="J7" s="16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="26" t="s">
         <v>35</v>
@@ -1733,226 +1733,221 @@
       <c r="L7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M7" s="23">
-        <v>5</v>
+      <c r="M7" s="22">
+        <v>9</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" spans="1:14">
-      <c r="A8" s="3">
+    <row r="8" s="4" customFormat="1" spans="1:14">
+      <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>4</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" s="25" t="s">
+      <c r="H8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="25" t="s">
+      <c r="L8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="20">
+      <c r="M8" s="22">
         <v>3</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" spans="1:14">
-      <c r="A9" s="3">
+    <row r="9" s="5" customFormat="1" spans="1:14">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>5</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="25" t="s">
+      <c r="H9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="25" t="s">
+      <c r="L9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="8">
         <v>2</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" spans="1:14">
-      <c r="A10" s="3">
+    <row r="10" s="4" customFormat="1" spans="1:14">
+      <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>6</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="25" t="s">
+      <c r="E10" s="20"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="22">
         <v>1</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" spans="1:14">
-      <c r="A11" s="3">
+    <row r="11" s="4" customFormat="1" spans="1:14">
+      <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>7</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="20"/>
+      <c r="F11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="25" t="s">
+      <c r="H11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="22">
         <v>3</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" spans="1:14">
-      <c r="A12" s="3">
+    <row r="12" spans="1:14">
+      <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="5">
         <v>8</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="25" t="s">
+      <c r="H12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="25" t="s">
+      <c r="L12" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="22">
         <v>1</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N12" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" spans="1:14">
-      <c r="F13" s="21"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="23"/>
+    <row r="13" s="5" customFormat="1" spans="1:14">
+      <c r="E13" s="6"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="popUpConfig" sheetId="1" r:id="rId1"/>
@@ -56,6 +56,8 @@
 3. 游戏ID：warehouse.xlsx 读取该表中的&lt;gameID&gt;字段值
 4. 是功能同时也是活动  配置warehouse.xlsx 读取该表中的&lt;ID&gt;字段值
 描述：配置多个功能弹窗时，随机一个弹出；仅配置一个 则必弹；
+5. 手机绑定弹窗
+99.纯弹窗&amp;外部链接跳转URL
 参数例子：
    1_11       //类型ID_对应功能ID
 或 1_11;2_9  // 类型ID1_对应功能ID1;类型ID2_对应功能ID2</t>
@@ -111,12 +113,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+URL仅匹配 类型为 “ 99” 的</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+有值显示帮助文本按钮，反之  不显示帮助按钮</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
   <si>
     <t>序号ID</t>
   </si>
@@ -157,6 +203,12 @@
     <t>每天弹窗次数</t>
   </si>
   <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>帮助文本</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -211,6 +263,12 @@
     <t>count</t>
   </si>
   <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>help</t>
+  </si>
+  <si>
     <t>4_106</t>
   </si>
   <si>
@@ -311,6 +369,36 @@
   </si>
   <si>
     <t>买一送七</t>
+  </si>
+  <si>
+    <t>99_0</t>
+  </si>
+  <si>
+    <t>纯弹窗&amp;外部链接</t>
+  </si>
+  <si>
+    <t>tanchuang_res/%s/tanchuang-test1.png</t>
+  </si>
+  <si>
+    <t>2025/12/1 0:00:00</t>
+  </si>
+  <si>
+    <t>2026/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>满足开启及时间有效条件内就弹出</t>
+  </si>
+  <si>
+    <t>5_0</t>
+  </si>
+  <si>
+    <t>手机绑定弹窗</t>
+  </si>
+  <si>
+    <t>2036/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>没有绑定手机号则弹出，绑定了就不弹出</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -398,7 +486,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +514,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -442,6 +536,13 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -588,12 +689,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -931,138 +1032,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1081,23 +1182,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -1106,7 +1210,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1129,7 +1233,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1191,6 +1304,15 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1450,511 +1572,621 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
-    <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="6" customWidth="1"/>
+    <col min="3" max="3" width="35.5833333333333" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="57.375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="72.35" style="6" customWidth="1"/>
     <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
     <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
-    <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="8" customWidth="1"/>
-    <col min="14" max="14" width="72.125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="5"/>
-    <col min="16" max="16" width="19.875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.75" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9" style="5"/>
-    <col min="19" max="19" width="9.375" style="5"/>
-    <col min="20" max="20" width="23.25" style="5" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="5"/>
+    <col min="9" max="9" width="16.25" style="6" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="20.8833333333333" style="8" customWidth="1"/>
+    <col min="12" max="12" width="21.175" style="8" customWidth="1"/>
+    <col min="13" max="15" width="12.875" style="9" customWidth="1"/>
+    <col min="16" max="16" width="72.125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="9.375" style="6"/>
+    <col min="18" max="18" width="19.875" style="6" customWidth="1"/>
+    <col min="19" max="19" width="13.75" style="6" customWidth="1"/>
+    <col min="20" max="20" width="9" style="6"/>
+    <col min="21" max="21" width="9.375" style="6"/>
+    <col min="22" max="22" width="23.25" style="6" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="2" customFormat="1" ht="15" spans="1:16">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="15" t="s">
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:16">
+      <c r="A2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="E2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="F2" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A3" s="9" t="s">
+      <c r="H2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="I2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9" t="s">
+      <c r="L2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:16">
+      <c r="A3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="B3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="G3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="H3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="J3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="K3" s="14" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:14">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="14"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="5">
+      <c r="L3" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:16">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="16" t="b">
+      <c r="I5" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="8">
+      <c r="K5" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="9">
         <v>3</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:14">
+      <c r="P5" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:16">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="18" t="s">
+      <c r="L6" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="M6" s="21">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21"/>
+      <c r="O6" s="21"/>
+      <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="20">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:14">
+    </row>
+    <row r="7" s="4" customFormat="1" spans="1:16">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D7" s="4">
-        <v>3</v>
-      </c>
-      <c r="E7" s="21"/>
+        <v>5</v>
+      </c>
+      <c r="E7" s="22"/>
       <c r="F7" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="16" t="b">
+        <v>50</v>
+      </c>
+      <c r="H7" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="17" t="b">
+      <c r="I7" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="16" t="b">
+      <c r="J7" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="23">
+      <c r="K7" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="24">
         <v>5</v>
       </c>
-      <c r="N7" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" spans="1:14">
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:16">
       <c r="A8" s="3">
         <v>4</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
-      </c>
-      <c r="E8" s="18"/>
+        <v>6</v>
+      </c>
+      <c r="E8" s="19"/>
       <c r="F8" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="17" t="b">
+        <v>54</v>
+      </c>
+      <c r="H8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="17" t="b">
+      <c r="I8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="17" t="b">
+      <c r="J8" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="20">
+      <c r="K8" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="21">
         <v>3</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:14">
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:16">
       <c r="A9" s="3">
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D9" s="3">
-        <v>5</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>53</v>
+        <v>7</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="17" t="b">
+        <v>58</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="17" t="b">
+      <c r="I9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="17" t="b">
+      <c r="J9" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="20">
+      <c r="K9" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="21">
         <v>2</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:14">
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:16">
       <c r="A10" s="3">
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D10" s="3">
-        <v>6</v>
-      </c>
-      <c r="E10" s="18"/>
+        <v>8</v>
+      </c>
+      <c r="E10" s="19"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="17" t="b">
+      <c r="H10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="17" t="b">
+      <c r="I10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="17" t="b">
+      <c r="J10" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="20">
+      <c r="K10" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="21">
         <v>1</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:14">
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:16">
       <c r="A11" s="3">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3">
-        <v>7</v>
-      </c>
-      <c r="E11" s="18"/>
+        <v>9</v>
+      </c>
+      <c r="E11" s="19"/>
       <c r="F11" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="20">
+      <c r="M11" s="21">
         <v>3</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:14">
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:16">
       <c r="A12" s="3">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D12" s="3">
-        <v>8</v>
-      </c>
-      <c r="E12" s="18"/>
+        <v>10</v>
+      </c>
+      <c r="E12" s="19"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="17" t="b">
+      <c r="H12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="17" t="b">
+      <c r="I12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="17" t="b">
+      <c r="J12" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" s="20">
+      <c r="K12" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="21">
         <v>1</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="1" spans="1:14">
-      <c r="F13" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="1:16">
+      <c r="A13" s="4">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="22"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="23"/>
+      <c r="H13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" s="24">
+        <v>99</v>
+      </c>
+      <c r="N13" s="25"/>
+      <c r="O13" s="22">
+        <v>3021029</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" spans="1:16">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="5"/>
+      <c r="H14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="27">
+        <v>99</v>
+      </c>
+      <c r="N14" s="27"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="5" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="O13">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1973,42 +2205,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2031,20 +2263,20 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2061,20 +2293,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2091,20 +2323,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2121,20 +2353,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2151,22 +2383,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2183,10 +2415,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2209,17 +2441,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -383,7 +383,7 @@
     <t>2025/12/1 0:00:00</t>
   </si>
   <si>
-    <t>2026/12/31 23:59:59</t>
+    <t>2025/12/31 23:59:59</t>
   </si>
   <si>
     <t>满足开启及时间有效条件内就弹出</t>
@@ -486,7 +486,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -514,12 +514,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -540,6 +534,7 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1032,138 +1027,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1182,26 +1177,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
@@ -1210,7 +1202,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -1233,16 +1225,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
@@ -1575,73 +1561,73 @@
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="6" customWidth="1"/>
-    <col min="2" max="2" width="30.75" style="6" customWidth="1"/>
-    <col min="3" max="3" width="35.5833333333333" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14.625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="57.375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="72.35" style="6" customWidth="1"/>
+    <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="35.5833333333333" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
     <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
     <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.25" style="6" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="20.8833333333333" style="8" customWidth="1"/>
-    <col min="12" max="12" width="21.175" style="8" customWidth="1"/>
-    <col min="13" max="15" width="12.875" style="9" customWidth="1"/>
-    <col min="16" max="16" width="72.125" style="6" customWidth="1"/>
-    <col min="17" max="17" width="9.375" style="6"/>
-    <col min="18" max="18" width="19.875" style="6" customWidth="1"/>
-    <col min="19" max="19" width="13.75" style="6" customWidth="1"/>
-    <col min="20" max="20" width="9" style="6"/>
-    <col min="21" max="21" width="9.375" style="6"/>
-    <col min="22" max="22" width="23.25" style="6" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="6"/>
+    <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
+    <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
+    <col min="13" max="15" width="12.875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="72.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="9.375" style="5"/>
+    <col min="18" max="18" width="19.875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="13.75" style="5" customWidth="1"/>
+    <col min="20" max="20" width="9" style="5"/>
+    <col min="21" max="21" width="9.375" style="5"/>
+    <col min="22" max="22" width="23.25" style="5" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="15" spans="1:16">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="14" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -1649,150 +1635,150 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="15" spans="1:16">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="9"/>
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:16">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="15" t="s">
+      <c r="N3" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="15" t="s">
+      <c r="O3" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:16">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>3</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>37</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="17" t="b">
+      <c r="H5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="I5" s="18" t="b">
+      <c r="I5" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J5" s="17" t="b">
+      <c r="J5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="K5" s="28" t="s">
+      <c r="K5" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="8">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1809,7 +1795,7 @@
       <c r="D6" s="3">
         <v>4</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1818,26 +1804,26 @@
       <c r="G6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="18" t="b">
+      <c r="H6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="18" t="b">
+      <c r="I6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="18" t="b">
+      <c r="J6" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="M6" s="21">
+      <c r="M6" s="20">
         <v>1</v>
       </c>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
       <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
@@ -1855,33 +1841,33 @@
       <c r="D7" s="4">
         <v>5</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="17" t="b">
+      <c r="H7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="18" t="b">
+      <c r="I7" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="17" t="b">
+      <c r="J7" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="K7" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="L7" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="23">
         <v>5</v>
       </c>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
       <c r="P7" s="4" t="s">
         <v>41</v>
       </c>
@@ -1899,33 +1885,33 @@
       <c r="D8" s="3">
         <v>6</v>
       </c>
-      <c r="E8" s="19"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="18" t="b">
+      <c r="H8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="b">
+      <c r="I8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="18" t="b">
+      <c r="J8" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="20">
         <v>3</v>
       </c>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
       <c r="P8" s="3" t="s">
         <v>41</v>
       </c>
@@ -1943,35 +1929,35 @@
       <c r="D9" s="3">
         <v>7</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="18" t="s">
         <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="18" t="b">
+      <c r="H9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="18" t="b">
+      <c r="I9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="18" t="b">
+      <c r="J9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M9" s="20">
         <v>2</v>
       </c>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
       <c r="P9" s="3" t="s">
         <v>41</v>
       </c>
@@ -1989,29 +1975,29 @@
       <c r="D10" s="3">
         <v>8</v>
       </c>
-      <c r="E10" s="19"/>
+      <c r="E10" s="18"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="18" t="b">
+      <c r="H10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="18" t="b">
+      <c r="I10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="18" t="b">
+      <c r="J10" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="21">
+      <c r="M10" s="20">
         <v>1</v>
       </c>
-      <c r="N10" s="21"/>
-      <c r="O10" s="21"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
       <c r="P10" s="3" t="s">
         <v>41</v>
       </c>
@@ -2029,33 +2015,33 @@
       <c r="D11" s="3">
         <v>9</v>
       </c>
-      <c r="E11" s="19"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="18" t="b">
+      <c r="H11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="18" t="b">
+      <c r="I11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="18" t="b">
+      <c r="J11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M11" s="20">
         <v>3</v>
       </c>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
       <c r="P11" s="3" t="s">
         <v>41</v>
       </c>
@@ -2073,113 +2059,111 @@
       <c r="D12" s="3">
         <v>10</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="18"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="18" t="b">
+      <c r="H12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="18" t="b">
+      <c r="I12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="18" t="b">
+      <c r="J12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="20">
         <v>1</v>
       </c>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
       <c r="P12" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" spans="1:16">
-      <c r="A13" s="4">
+    <row r="13" s="3" customFormat="1" spans="1:16">
+      <c r="A13" s="3">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="4"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="3"/>
       <c r="H13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" s="20">
+        <v>99</v>
+      </c>
+      <c r="N13" s="24"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:16">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="I13" s="18" t="b">
+      <c r="E14" s="21"/>
+      <c r="F14" s="4"/>
+      <c r="H14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J13" s="17" t="b">
+      <c r="J14" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K14" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="L13" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="24">
+      <c r="L14" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="23">
         <v>99</v>
       </c>
-      <c r="N13" s="25"/>
-      <c r="O13" s="22">
-        <v>3021029</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" s="5" customFormat="1" spans="1:16">
-      <c r="A14" s="5">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="5"/>
-      <c r="H14" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" s="27">
-        <v>99</v>
-      </c>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="5" t="s">
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="4" t="s">
         <v>78</v>
       </c>
     </row>

--- a/hall/resources/sample/popUpConfig.xlsx
+++ b/hall/resources/sample/popUpConfig.xlsx
@@ -56,6 +56,8 @@
 3. 游戏ID：warehouse.xlsx 读取该表中的&lt;gameID&gt;字段值
 4. 是功能同时也是活动  配置warehouse.xlsx 读取该表中的&lt;ID&gt;字段值
 描述：配置多个功能弹窗时，随机一个弹出；仅配置一个 则必弹；
+5. 手机绑定弹窗
+99.纯弹窗&amp;外部链接跳转URL
 参数例子：
    1_11       //类型ID_对应功能ID
 或 1_11;2_9  // 类型ID1_对应功能ID1;类型ID2_对应功能ID2</t>
@@ -111,12 +113,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+URL仅匹配 类型为 “ 99” 的</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+有值显示帮助文本按钮，反之  不显示帮助按钮</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
   <si>
     <t>序号ID</t>
   </si>
@@ -157,6 +203,12 @@
     <t>每天弹窗次数</t>
   </si>
   <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>帮助文本</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -211,6 +263,12 @@
     <t>count</t>
   </si>
   <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>help</t>
+  </si>
+  <si>
     <t>4_106</t>
   </si>
   <si>
@@ -311,6 +369,36 @@
   </si>
   <si>
     <t>买一送七</t>
+  </si>
+  <si>
+    <t>99_0</t>
+  </si>
+  <si>
+    <t>纯弹窗&amp;外部链接</t>
+  </si>
+  <si>
+    <t>tanchuang_res/%s/tanchuang-test1.png</t>
+  </si>
+  <si>
+    <t>2025/12/1 0:00:00</t>
+  </si>
+  <si>
+    <t>2025/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>满足开启及时间有效条件内就弹出</t>
+  </si>
+  <si>
+    <t>5_0</t>
+  </si>
+  <si>
+    <t>手机绑定弹窗</t>
+  </si>
+  <si>
+    <t>2036/12/31 23:59:59</t>
+  </si>
+  <si>
+    <t>没有绑定手机号则弹出，绑定了就不弹出</t>
   </si>
   <si>
     <t>每日奖金(原月卡)：UIDailyBonus</t>
@@ -398,7 +486,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,12 +503,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -442,6 +530,14 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -931,138 +1027,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1110,6 +1206,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1128,7 +1225,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1191,6 +1290,15 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="常规 80" xfId="49"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1450,7 +1558,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="5" customWidth="1"/>
@@ -1459,24 +1567,24 @@
     <col min="4" max="4" width="14.625" style="5" customWidth="1"/>
     <col min="5" max="5" width="57.375" style="6" customWidth="1"/>
     <col min="6" max="6" width="72.35" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.525" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="48.525" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.875" style="4" customWidth="1"/>
     <col min="9" max="9" width="16.25" style="5" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="5" customWidth="1"/>
     <col min="11" max="11" width="20.8833333333333" style="7" customWidth="1"/>
     <col min="12" max="12" width="21.175" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="8" customWidth="1"/>
-    <col min="14" max="14" width="72.125" style="5" customWidth="1"/>
-    <col min="15" max="15" width="9.375" style="5"/>
-    <col min="16" max="16" width="19.875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.75" style="5" customWidth="1"/>
-    <col min="18" max="18" width="9" style="5"/>
-    <col min="19" max="19" width="9.375" style="5"/>
-    <col min="20" max="20" width="23.25" style="5" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="5"/>
+    <col min="13" max="15" width="12.875" style="8" customWidth="1"/>
+    <col min="16" max="16" width="72.125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="9.375" style="5"/>
+    <col min="18" max="18" width="19.875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="13.75" style="5" customWidth="1"/>
+    <col min="20" max="20" width="9" style="5"/>
+    <col min="21" max="21" width="9.375" style="5"/>
+    <col min="22" max="22" width="23.25" style="5" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" ht="15" spans="1:14">
+    <row r="1" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1516,89 +1624,107 @@
       <c r="M1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="15" spans="1:14">
+    <row r="2" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A2" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="12" t="s">
+      <c r="N2" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="15" spans="1:14">
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A3" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="15" spans="1:14">
+        <v>32</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="15" spans="1:16">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1612,344 +1738,439 @@
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
       <c r="M4" s="14"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="5">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D5" s="5">
+        <v>3</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="16" t="b">
+      <c r="I5" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="16" t="b">
-        <v>0</v>
-      </c>
       <c r="J5" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="24" t="s">
-        <v>36</v>
+        <v>1</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>40</v>
       </c>
       <c r="M5" s="8">
         <v>3</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" spans="1:14">
+      <c r="P5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" spans="1:16">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="L6" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="M6" s="20">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="19">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" s="4" customFormat="1" spans="1:14">
+    </row>
+    <row r="7" s="4" customFormat="1" spans="1:16">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D7" s="4">
+        <v>5</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="23">
+        <v>5</v>
+      </c>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" spans="1:16">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="20">
         <v>3</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="16" t="b">
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:16">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="16" t="b">
+      <c r="I9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J7" s="16" t="b">
+      <c r="J9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="22">
+      <c r="K9" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="20">
+        <v>2</v>
+      </c>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:16">
+      <c r="A10" s="3">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3">
+        <v>8</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="20">
+        <v>1</v>
+      </c>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:16">
+      <c r="A11" s="3">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="3">
         <v>9</v>
       </c>
-      <c r="N7" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" spans="1:14">
-      <c r="A8" s="4">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="4">
-        <v>4</v>
-      </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="16" t="b">
+      <c r="E11" s="18"/>
+      <c r="F11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="16" t="b">
+      <c r="I11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="16" t="b">
+      <c r="J11" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="22">
+      <c r="K11" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="20">
         <v>3</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="1" spans="1:14">
-      <c r="A9" s="5">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="16" t="b">
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:16">
+      <c r="A12" s="3">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3">
+        <v>10</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="16" t="b">
+      <c r="I12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="16" t="b">
+      <c r="J12" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K9" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="8">
+      <c r="K12" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="20">
+        <v>1</v>
+      </c>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" s="3" customFormat="1" spans="1:16">
+      <c r="A13" s="3">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="1" spans="1:14">
-      <c r="A10" s="4">
-        <v>6</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="4">
-        <v>6</v>
-      </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="16" t="b">
+      <c r="E13" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="16" t="b">
+      <c r="I13" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="16" t="b">
+      <c r="J13" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="K10" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="22">
+      <c r="K13" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" s="20">
+        <v>99</v>
+      </c>
+      <c r="N13" s="24"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" spans="1:16">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="N10" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="1" spans="1:14">
-      <c r="A11" s="4">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="4">
-        <v>7</v>
-      </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="16" t="b">
+      <c r="E14" s="21"/>
+      <c r="F14" s="4"/>
+      <c r="H14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="22">
-        <v>3</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="5">
-        <v>8</v>
-      </c>
-      <c r="H12" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M12" s="22">
+      <c r="J14" s="16" t="b">
         <v>1</v>
       </c>
-      <c r="N12" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" s="5" customFormat="1" spans="1:14">
-      <c r="E13" s="6"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="8"/>
+      <c r="K14" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="23">
+        <v>99</v>
+      </c>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="O13">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1968,42 +2189,42 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2026,20 +2247,20 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -2056,20 +2277,20 @@
         <v>2</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -2086,20 +2307,20 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1">
         <v>4</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -2116,20 +2337,20 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -2146,22 +2367,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D14" s="1">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -2178,10 +2399,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1">
         <v>6</v>
@@ -2204,17 +2425,17 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1">
         <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
